--- a/registration_forms/035_employee_wellbeing_strategy_forum_registration_form--registration_forms.xlsx
+++ b/registration_forms/035_employee_wellbeing_strategy_forum_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Form Category</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Form Description</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_name</t>
+          <t>form_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Form Name</t>
+          <t>Form Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Form Description 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
